--- a/Noyabrsk/Справка_ППД_Noyabrsk.xlsx
+++ b/Noyabrsk/Справка_ППД_Noyabrsk.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:J41"/>
+  <dimension ref="A2:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -538,267 +538,70 @@
       </c>
     </row>
     <row r="12"/>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>КНС-1А Спорышевское м/р</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>насос</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ЦНС 240-1650-2ТМ </t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>НА-5 СО</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>20093/002-2</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>61000387815</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>2</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>КНС-1А Спорышевское м/р</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>насос</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>ЦНС 240-1660-2ТМ</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>НА-6 СО</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>7</v>
-      </c>
-      <c r="J15" t="n">
-        <v>61000111457</v>
-      </c>
-    </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>3</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>№ п/п</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>КНС-1А Спорышевское м/р</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>насос</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>ЦНС 240-1650-2ИТ</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>НА-7 СО</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>26</v>
-      </c>
-      <c r="J16" t="n">
-        <v>61000235346</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>КНС-1А Спорышевское м/р</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>насос</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ЦНС 240-1660-2ТМ</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>НА-14 СО</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>002-3</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>61000310495</v>
-      </c>
-    </row>
+          <t>ЦЕХ</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>Работы по текущему ремонту</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Дата выполнения работ</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Подпись, ФИО механика (мастера)</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>№ ЗАКАЗА САП ТОРО</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
-      <c r="A18" t="n">
-        <v>5</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>КНС-1Б Спорышевское м/р</t>
+          <t>Объект</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>насос</t>
+          <t>Оборудование</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>НЦНС-К-310-1510-УХЛ4</t>
+          <t>Марка оборудования</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>НА-9 СО</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>885</v>
-      </c>
-      <c r="J18" t="n">
-        <v>61000173330</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>6</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>КНС-1Б Спорышевское м/р</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>насос</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>ЦНС 240-1650-2ТМ</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>НА-10 СО</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>86</v>
-      </c>
-      <c r="J19" t="n">
-        <v>61000235329</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>7</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>КНС-1В Спорышевское м/р</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>насос</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>ЦНС 240-1050-2ТМ</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>НА-11 СО</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>20086/002-1</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>61000312019</v>
-      </c>
-    </row>
+          <t>Рег. №</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Зав №</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="21">
       <c r="A21" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -807,7 +610,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>КНС-1В Спорышевское м/р</t>
+          <t>КНС-4 Пограничное м/р</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -817,26 +620,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ЦНС 240-1050-2ИТ</t>
+          <t>НЦС 320-1350-1561-УХЛ4</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>НА-13 СО</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+          <t>НА-2 ТР</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>2187</v>
       </c>
       <c r="J21" t="n">
-        <v>61000153881</v>
+        <v>61000188892</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -845,7 +646,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>КНС-3 Спорышевское м/р</t>
+          <t>КНС-4 Пограничное м/р</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -855,24 +656,26 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ЦНС 240-1660-2ТМ</t>
+          <t>ЦНС 240-1422-2ТМ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>НА-1 СО</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>2</v>
+          <t>НА-4 ТР</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>20062/004-4</t>
+        </is>
       </c>
       <c r="J22" t="n">
-        <v>61000294385</v>
+        <v>61000188908</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -881,7 +684,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>КНС-3 Спорышевское м/р</t>
+          <t>КНС-2 Холмогорское м/р_ЯНАО</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -891,24 +694,26 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>НЦС К 310-1510-УХЛ4</t>
+          <t>ЦНС 180-1422-2ТМ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>НА-2 СО</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>2070</v>
+          <t>НА-8 ТР</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>20091/001-2</t>
+        </is>
       </c>
       <c r="J23" t="n">
-        <v>61000113163</v>
+        <v>61000173553</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -917,7 +722,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>КНС-3 Спорышевское м/р</t>
+          <t>КНС-2 Холмогорское м/р_ЯНАО</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -927,24 +732,26 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ЦНСс 310-1510-ПП-К-Т1-УХЛ4</t>
+          <t>ЦНС 240-1422-2ИТ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>НА-3 СО</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>25074002096</v>
+          <t>НА-11 ТР</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>240-23</t>
+        </is>
       </c>
       <c r="J24" t="n">
-        <v>61000533266</v>
+        <v>61000310510</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -953,7 +760,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>КНС-3 Спорышевское м/р</t>
+          <t>КНС Средне-Итурское м/р</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -963,330 +770,157 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ЦНС 310-1510-2И1Т</t>
+          <t>ЦНС 240-1422-2ИТ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>НА-4 СО</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>240-28</t>
-        </is>
+          <t>НА-1 ТР</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>11</v>
       </c>
       <c r="J25" t="n">
-        <v>61000313869</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+        <v>61000173482</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>№ п/п</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>ЦЕХ</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>Работы по текущему ремонту</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Работы по замене агрегатов</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t>Дата выполнения работ</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>Подпись, ФИО механика (мастера)</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>№ ЗАКАЗА САП ТОРО</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="C30" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Оборудование</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Рег. №</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Демонтаж</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Монтаж/ПНР</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>Марка оборудования</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Рег. №</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Зав №</t>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="33">
-      <c r="A33" t="n">
+    </row>
+    <row r="30"/>
+    <row r="32">
+      <c r="A32" t="n">
         <v>1</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>ЦППД-1</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>КНС-1 Карамовское м/р</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>насос</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>ЦНСс-310-1510-ПП-К-Т1-УХЛ4</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>НА-1 ТР</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>25074002097</v>
-      </c>
-      <c r="J33" t="n">
-        <v>61000533265</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>2</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>КНС-3 Холмогорское м/р_ХМАО</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>насос</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>ЦНС 240-1422-2ТМ</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>НА-7 ТР</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>10</v>
-      </c>
-      <c r="J34" t="n">
-        <v>61000173560</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>3</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>КНС-1А Спорышевское м/р</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>насос</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>НЦС 240-1650-15061-УХЛ4</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>НА-8 ТР</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>2422</v>
-      </c>
-      <c r="J35" t="n">
-        <v>61000491174</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>4</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>КНС Средне-Итурское м/р</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>насос</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>ЦНС 180-1422Мт</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>НА-5 ТР</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>338</v>
-      </c>
-      <c r="J36" t="n">
-        <v>61000387520</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>№ п/п</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>ЦЕХ</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>Работы по замене агрегатов</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Дата выполнения работ</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Подпись, ФИО механика (мастера)</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>№ ЗАКАЗА САП ТОРО</t>
-        </is>
-      </c>
-    </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Объект</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Рег. №</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Демонтаж</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Монтаж/ПНР</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Марка оборудования</t>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>КНС-1В Спорышевское м/р</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>НА-12</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1-2689</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ЦНС 240-1050-2ИТЦ</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>61000113296</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="H38:H41"/>
+    <mergeCell ref="I27:I30"/>
+    <mergeCell ref="C29:C30"/>
     <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E29:E30"/>
     <mergeCell ref="D11:D12"/>
+    <mergeCell ref="I16:I19"/>
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="A16:A19"/>
     <mergeCell ref="H9:H12"/>
+    <mergeCell ref="F18:F19"/>
     <mergeCell ref="J9:J12"/>
     <mergeCell ref="H5"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="I28:I31"/>
+    <mergeCell ref="J27:J30"/>
+    <mergeCell ref="C27:G28"/>
     <mergeCell ref="F4"/>
-    <mergeCell ref="J28:J31"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="E11:E12"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="B28:B31"/>
-    <mergeCell ref="C38:G39"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="A27:A30"/>
     <mergeCell ref="B9:B12"/>
-    <mergeCell ref="C28:G29"/>
+    <mergeCell ref="D18:D19"/>
     <mergeCell ref="F3"/>
-    <mergeCell ref="I38:I41"/>
-    <mergeCell ref="H28:H31"/>
+    <mergeCell ref="H16:H19"/>
+    <mergeCell ref="J16:J19"/>
     <mergeCell ref="F11:F12"/>
-    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="H27:H30"/>
+    <mergeCell ref="F29:F30"/>
     <mergeCell ref="A9:A12"/>
     <mergeCell ref="D6:I6"/>
     <mergeCell ref="F2"/>
-    <mergeCell ref="A38:A41"/>
     <mergeCell ref="I9:I12"/>
-    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="C16:G17"/>
     <mergeCell ref="G11:G12"/>
-    <mergeCell ref="J38:J41"/>
-    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="B16:B19"/>
     <mergeCell ref="C9:G10"/>
-    <mergeCell ref="D40:D41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
